--- a/Cost/Cost.xlsx
+++ b/Cost/Cost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="305" documentId="8_{2ED45462-44C2-47F0-8A13-4996CA137E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81403DB4-F72F-4F78-A69F-EBF2C910F6EC}"/>
+  <xr:revisionPtr revIDLastSave="1525" documentId="8_{2ED45462-44C2-47F0-8A13-4996CA137E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDCF31AE-08E1-4167-B9DA-0D41B0DC70BF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
+    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>6.8565259664597198</v>
+        <v>17.139772197806899</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
@@ -590,7 +590,7 @@
       </c>
       <c r="B8">
         <f>SUM(B2:B7)</f>
-        <v>46.108383838401764</v>
+        <v>56.391630069748942</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>

--- a/Cost/Cost.xlsx
+++ b/Cost/Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22464" documentId="8_{2ED45462-44C2-47F0-8A13-4996CA137E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{506DCAA1-340F-4B72-ACE6-08B4AA29924D}"/>
+  <xr:revisionPtr revIDLastSave="55640" documentId="8_{2ED45462-44C2-47F0-8A13-4996CA137E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31506C56-364B-4EF5-A6E0-263D3BE3F896}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>cost_lid</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>Total_Variable_Cost</t>
+  </si>
+  <si>
+    <t>&lt; $</t>
   </si>
 </sst>
 </file>
@@ -480,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1A7304-AB3A-4B8B-82AA-38816B5F8F53}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" customWidth="1"/>
@@ -506,7 +509,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>8.3788199260252707</v>
+        <v>5.4178783858815702</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -526,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>12.341746739627499</v>
+        <v>1.7132624999999999</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
@@ -546,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>28.35</v>
+        <v>94.5</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
@@ -566,7 +569,7 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>8.8994694900443996</v>
+        <v>8.8993031997326408</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
@@ -602,7 +605,7 @@
       </c>
       <c r="B8">
         <f>SUM(B2:B5)</f>
-        <v>57.970036155697173</v>
+        <v>110.53044408561421</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
@@ -613,6 +616,11 @@
       <c r="G8">
         <f>G6 / B6</f>
         <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Cost/Cost.xlsx
+++ b/Cost/Cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Cost/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="863" documentId="8_{2ED45462-44C2-47F0-8A13-4996CA137E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B58B25F3-3F17-4CD0-B8BC-85A6697378EF}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4C850D2-A81F-4316-B7D2-2F389F444903}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
+    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <definedName name="Battery_Cost_USD">Sheet1!$B$4</definedName>
     <definedName name="cost_lid">Sheet1!$B$3</definedName>
     <definedName name="Total_Cost">Sheet1!$B$8</definedName>
+    <definedName name="UNC_Compliance_Fixed">Sheet1!$B$12</definedName>
+    <definedName name="UNC_MFG_Fixed">Sheet1!$B$13</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
   <si>
     <t>cost_lid</t>
   </si>
@@ -92,6 +94,24 @@
   </si>
   <si>
     <t>Total_Variable_Cost</t>
+  </si>
+  <si>
+    <t>Uncertainty</t>
+  </si>
+  <si>
+    <t>% Cost Fluctuation</t>
+  </si>
+  <si>
+    <t>Adjusted</t>
+  </si>
+  <si>
+    <t>Base Value</t>
+  </si>
+  <si>
+    <t>UNC_Compliance_Fixed</t>
+  </si>
+  <si>
+    <t>UNC_MFG_Fixed</t>
   </si>
 </sst>
 </file>
@@ -480,14 +500,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1A7304-AB3A-4B8B-82AA-38816B5F8F53}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
     <col min="6" max="6" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -500,13 +522,19 @@
       <c r="F1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>2.0065108174152999</v>
+        <v>2.00238838189764</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -521,7 +549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -535,13 +563,17 @@
         <v>7</v>
       </c>
       <c r="G3">
+        <f>I3*B13</f>
         <v>80000</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -561,29 +593,33 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5">
-        <v>8.8994694900443996</v>
+        <v>8.9119495779417992</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5">
+        <f>I5*B12</f>
         <v>25000</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -596,13 +632,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8">
         <f>SUM(B2:B5)</f>
-        <v>46.112506273919422</v>
+        <v>46.120863926299158</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
@@ -610,9 +646,36 @@
       <c r="F8" t="s">
         <v>15</v>
       </c>
-      <c r="G8" t="e">
+      <c r="G8">
         <f>G6 / B6</f>
-        <v>#DIV/0!</v>
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Cost/Cost.xlsx
+++ b/Cost/Cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4C850D2-A81F-4316-B7D2-2F389F444903}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64B149BE-1D07-4509-9A22-B58A0C5ED6C1}"/>
   <bookViews>
-    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
+    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,12 @@
   <definedNames>
     <definedName name="Battery_Cost_USD">Sheet1!$B$4</definedName>
     <definedName name="cost_lid">Sheet1!$B$3</definedName>
+    <definedName name="Demand">Sheet1!$B$16</definedName>
     <definedName name="Total_Cost">Sheet1!$B$8</definedName>
     <definedName name="UNC_Compliance_Fixed">Sheet1!$B$12</definedName>
+    <definedName name="UNC_Demand_Variation">Sheet1!$B$17</definedName>
     <definedName name="UNC_MFG_Fixed">Sheet1!$B$13</definedName>
+    <definedName name="UNC_Testing_Fixed">Sheet1!$B$14</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>cost_lid</t>
   </si>
@@ -112,6 +115,21 @@
   </si>
   <si>
     <t>UNC_MFG_Fixed</t>
+  </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>raw demand</t>
+  </si>
+  <si>
+    <t>UNC_Demand_Variation</t>
+  </si>
+  <si>
+    <t>% variation</t>
+  </si>
+  <si>
+    <t>UNC_Testing_Fixed</t>
   </si>
 </sst>
 </file>
@@ -500,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C1A7304-AB3A-4B8B-82AA-38816B5F8F53}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -543,10 +561,14 @@
         <v>6</v>
       </c>
       <c r="G2">
+        <f>I2*B14</f>
         <v>25000</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
+      </c>
+      <c r="I2">
+        <v>25000</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -619,7 +641,8 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <f>_xlfn.CEILING.MATH((B17*B16), 100)</f>
+        <v>2000</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -648,7 +671,7 @@
       </c>
       <c r="G8">
         <f>G6 / B6</f>
-        <v>140000</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -676,6 +699,39 @@
       </c>
       <c r="C13" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16">
+        <v>1978.5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Cost/Cost.xlsx
+++ b/Cost/Cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Cost/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64B149BE-1D07-4509-9A22-B58A0C5ED6C1}"/>
+  <xr:revisionPtr revIDLastSave="70808" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D1A8612-6ACD-4329-B831-6145DD4380C7}"/>
   <bookViews>
-    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -552,7 +552,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>2.00238838189764</v>
+        <v>2.0010872535900699</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -562,7 +562,7 @@
       </c>
       <c r="G2">
         <f>I2*B14</f>
-        <v>25000</v>
+        <v>25441.187836277502</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>6.8565259664597198</v>
+        <v>6.7559497723649402</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
@@ -586,7 +586,7 @@
       </c>
       <c r="G3">
         <f>I3*B13</f>
-        <v>80000</v>
+        <v>78542.174808445605</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>28.35</v>
+        <v>29.0695887988965</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
@@ -620,14 +620,14 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>8.9119495779417992</v>
+        <v>9.0699028722732997</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5">
         <f>I5*B12</f>
-        <v>25000</v>
+        <v>25169.643927285502</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -649,7 +649,7 @@
       </c>
       <c r="G6">
         <f>SUM(G2:G5)</f>
-        <v>140000</v>
+        <v>139153.0065720086</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -661,7 +661,7 @@
       </c>
       <c r="B8">
         <f>SUM(B2:B5)</f>
-        <v>46.120863926299158</v>
+        <v>46.896528697124808</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
@@ -671,7 +671,7 @@
       </c>
       <c r="G8">
         <f>G6 / B6</f>
-        <v>70</v>
+        <v>69.576503286004296</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -684,7 +684,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>1.00678575709142</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -695,7 +695,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0.98177718510556999</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -706,7 +706,7 @@
         <v>27</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>1.0176475134511</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
@@ -728,7 +728,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>0.99871734801205903</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>

--- a/Cost/Cost.xlsx
+++ b/Cost/Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70808" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D1A8612-6ACD-4329-B831-6145DD4380C7}"/>
+  <xr:revisionPtr revIDLastSave="77738" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DED2F48-1138-4731-A53C-7EF8A7989675}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
   </bookViews>
@@ -552,7 +552,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>2.0010872535900699</v>
+        <v>1.9977588814889</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -562,7 +562,7 @@
       </c>
       <c r="G2">
         <f>I2*B14</f>
-        <v>25441.187836277502</v>
+        <v>24902.712079155874</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>6.7559497723649402</v>
+        <v>6.7821141759341304</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
@@ -586,7 +586,7 @@
       </c>
       <c r="G3">
         <f>I3*B13</f>
-        <v>78542.174808445605</v>
+        <v>79436.750971365444</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>29.0695887988965</v>
+        <v>28.890003953863999</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
@@ -620,14 +620,14 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>9.0699028722732997</v>
+        <v>8.5098240887779202</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5">
         <f>I5*B12</f>
-        <v>25169.643927285502</v>
+        <v>24724.424623266848</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -649,7 +649,7 @@
       </c>
       <c r="G6">
         <f>SUM(G2:G5)</f>
-        <v>139153.0065720086</v>
+        <v>139063.88767378815</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -661,7 +661,7 @@
       </c>
       <c r="B8">
         <f>SUM(B2:B5)</f>
-        <v>46.896528697124808</v>
+        <v>46.179701100064946</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
@@ -671,7 +671,7 @@
       </c>
       <c r="G8">
         <f>G6 / B6</f>
-        <v>69.576503286004296</v>
+        <v>69.531943836894072</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -684,7 +684,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>1.00678575709142</v>
+        <v>0.98897698493067399</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -695,7 +695,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0.98177718510556999</v>
+        <v>0.992959387142068</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -706,7 +706,7 @@
         <v>27</v>
       </c>
       <c r="B14">
-        <v>1.0176475134511</v>
+        <v>0.99610848316623501</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
@@ -728,7 +728,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0.99871734801205903</v>
+        <v>0.99655456954307098</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>

--- a/Cost/Cost.xlsx
+++ b/Cost/Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77738" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DED2F48-1138-4731-A53C-7EF8A7989675}"/>
+  <xr:revisionPtr revIDLastSave="77999" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4508E4B-6B4F-4329-B51D-09A9B72B606D}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
   </bookViews>
@@ -552,7 +552,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>1.9977588814889</v>
+        <v>1.99504251112199</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -562,7 +562,7 @@
       </c>
       <c r="G2">
         <f>I2*B14</f>
-        <v>24902.712079155874</v>
+        <v>24589.036011338849</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>6.7821141759341304</v>
+        <v>6.7821163439634597</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
@@ -586,7 +586,7 @@
       </c>
       <c r="G3">
         <f>I3*B13</f>
-        <v>79436.750971365444</v>
+        <v>80156.278554713601</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>28.890003953863999</v>
+        <v>5.6026195508792904</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
@@ -620,14 +620,14 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>8.5098240887779202</v>
+        <v>5.2908619402510499</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5">
         <f>I5*B12</f>
-        <v>24724.424623266848</v>
+        <v>24866.691429679249</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -642,14 +642,14 @@
       </c>
       <c r="B6">
         <f>_xlfn.CEILING.MATH((B17*B16), 100)</f>
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
       <c r="G6">
         <f>SUM(G2:G5)</f>
-        <v>139063.88767378815</v>
+        <v>139612.00599573168</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -661,7 +661,7 @@
       </c>
       <c r="B8">
         <f>SUM(B2:B5)</f>
-        <v>46.179701100064946</v>
+        <v>19.670640346215791</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
@@ -671,7 +671,7 @@
       </c>
       <c r="G8">
         <f>G6 / B6</f>
-        <v>69.531943836894072</v>
+        <v>1396.1200599573169</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -684,7 +684,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0.98897698493067399</v>
+        <v>0.99466765718716998</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -695,7 +695,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0.992959387142068</v>
+        <v>1.00195348193392</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -706,7 +706,7 @@
         <v>27</v>
       </c>
       <c r="B14">
-        <v>0.99610848316623501</v>
+        <v>0.98356144045355398</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
@@ -728,7 +728,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0.99655456954307098</v>
+        <v>1.26235293759229E-2</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>

--- a/Cost/Cost.xlsx
+++ b/Cost/Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77999" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4508E4B-6B4F-4329-B51D-09A9B72B606D}"/>
+  <xr:revisionPtr revIDLastSave="80906" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDCF1AA3-D6BA-43E3-A8CC-6B8BB52AAA18}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
   </bookViews>
@@ -552,7 +552,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>1.99504251112199</v>
+        <v>2.0138667419328198</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -562,7 +562,7 @@
       </c>
       <c r="G2">
         <f>I2*B14</f>
-        <v>24589.036011338849</v>
+        <v>25374.279620633501</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>6.7821163439634597</v>
+        <v>6.4752513622833696</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
@@ -586,7 +586,7 @@
       </c>
       <c r="G3">
         <f>I3*B13</f>
-        <v>80156.278554713601</v>
+        <v>80609.746279796804</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>5.6026195508792904</v>
+        <v>7.0875000000000004</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
@@ -620,14 +620,14 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>5.2908619402510499</v>
+        <v>8.4372690325080306</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5">
         <f>I5*B12</f>
-        <v>24866.691429679249</v>
+        <v>25052.313615230247</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -642,14 +642,14 @@
       </c>
       <c r="B6">
         <f>_xlfn.CEILING.MATH((B17*B16), 100)</f>
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
       <c r="G6">
         <f>SUM(G2:G5)</f>
-        <v>139612.00599573168</v>
+        <v>141036.33951566054</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -661,7 +661,7 @@
       </c>
       <c r="B8">
         <f>SUM(B2:B5)</f>
-        <v>19.670640346215791</v>
+        <v>24.013887136724222</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
@@ -671,7 +671,7 @@
       </c>
       <c r="G8">
         <f>G6 / B6</f>
-        <v>1396.1200599573169</v>
+        <v>705.18169757830265</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -684,7 +684,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0.99466765718716998</v>
+        <v>1.0020925446092099</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -695,7 +695,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>1.00195348193392</v>
+        <v>1.0076218284974601</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -706,7 +706,7 @@
         <v>27</v>
       </c>
       <c r="B14">
-        <v>0.98356144045355398</v>
+        <v>1.01497118482534</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
@@ -728,7 +728,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>1.26235293759229E-2</v>
+        <v>6.9342500785290404E-2</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>

--- a/Cost/Cost.xlsx
+++ b/Cost/Cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80906" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDCF1AA3-D6BA-43E3-A8CC-6B8BB52AAA18}"/>
+  <xr:revisionPtr revIDLastSave="89906" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2E07DA7-7725-434D-9CB9-78CD6C4D8128}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
   </bookViews>
@@ -552,7 +552,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>2.0138667419328198</v>
+        <v>1.9969953477374001</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -562,7 +562,7 @@
       </c>
       <c r="G2">
         <f>I2*B14</f>
-        <v>25374.279620633501</v>
+        <v>24942.965213645573</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>6.4752513622833696</v>
+        <v>6.6962978052113797</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
@@ -586,7 +586,7 @@
       </c>
       <c r="G3">
         <f>I3*B13</f>
-        <v>80609.746279796804</v>
+        <v>79427.911635241995</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>7.0875000000000004</v>
+        <v>25.000673015324399</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
@@ -620,14 +620,14 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>8.4372690325080306</v>
+        <v>3.6568889320404301</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5">
         <f>I5*B12</f>
-        <v>25052.313615230247</v>
+        <v>25385.2828164645</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -642,14 +642,14 @@
       </c>
       <c r="B6">
         <f>_xlfn.CEILING.MATH((B17*B16), 100)</f>
-        <v>200</v>
+        <v>1900</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
       <c r="G6">
         <f>SUM(G2:G5)</f>
-        <v>141036.33951566054</v>
+        <v>139756.15966535205</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -661,7 +661,7 @@
       </c>
       <c r="B8">
         <f>SUM(B2:B5)</f>
-        <v>24.013887136724222</v>
+        <v>37.350855100313609</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
@@ -671,7 +671,7 @@
       </c>
       <c r="G8">
         <f>G6 / B6</f>
-        <v>705.18169757830265</v>
+        <v>73.555873508080026</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -684,7 +684,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>1.0020925446092099</v>
+        <v>1.01541131265858</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -695,7 +695,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>1.0076218284974601</v>
+        <v>0.99284889544052501</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -706,7 +706,7 @@
         <v>27</v>
       </c>
       <c r="B14">
-        <v>1.01497118482534</v>
+        <v>0.99771860854582295</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
@@ -728,7 +728,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>6.9342500785290404E-2</v>
+        <v>0.91738890416793295</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>

--- a/Cost/Cost.xlsx
+++ b/Cost/Cost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Cost/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mbail\Documents\GitHub\ASE6002PEK\Cost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89906" documentId="114_{47B3782D-1062-4586-AE5B-422B5006DA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2E07DA7-7725-434D-9CB9-78CD6C4D8128}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F317413-22B4-478B-9307-5197B135CAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="11295" xr2:uid="{BC878E6E-4D73-4248-A308-30E2E8B17DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <definedName name="UNC_MFG_Fixed">Sheet1!$B$13</definedName>
     <definedName name="UNC_Testing_Fixed">Sheet1!$B$14</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="manual"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -195,10 +195,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -552,7 +548,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>1.9969953477374001</v>
+        <v>2.0065509547382998</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -562,7 +558,7 @@
       </c>
       <c r="G2">
         <f>I2*B14</f>
-        <v>24942.965213645573</v>
+        <v>25000</v>
       </c>
       <c r="H2" t="s">
         <v>1</v>
@@ -576,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>6.6962978052113797</v>
+        <v>62.422001821498398</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
@@ -586,7 +582,7 @@
       </c>
       <c r="G3">
         <f>I3*B13</f>
-        <v>79427.911635241995</v>
+        <v>80009.599999999991</v>
       </c>
       <c r="H3" t="s">
         <v>1</v>
@@ -600,7 +596,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>25.000673015324399</v>
+        <v>25.817608518610999</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
@@ -620,14 +616,14 @@
         <v>12</v>
       </c>
       <c r="B5">
-        <v>3.6568889320404301</v>
+        <v>7.2943605675288401</v>
       </c>
       <c r="F5" t="s">
         <v>9</v>
       </c>
       <c r="G5">
         <f>I5*B12</f>
-        <v>25385.2828164645</v>
+        <v>25004</v>
       </c>
       <c r="H5" t="s">
         <v>1</v>
@@ -642,14 +638,14 @@
       </c>
       <c r="B6">
         <f>_xlfn.CEILING.MATH((B17*B16), 100)</f>
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
       <c r="G6">
         <f>SUM(G2:G5)</f>
-        <v>139756.15966535205</v>
+        <v>140013.59999999998</v>
       </c>
       <c r="H6" t="s">
         <v>1</v>
@@ -661,7 +657,7 @@
       </c>
       <c r="B8">
         <f>SUM(B2:B5)</f>
-        <v>37.350855100313609</v>
+        <v>97.540521862376536</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
@@ -671,7 +667,7 @@
       </c>
       <c r="G8">
         <f>G6 / B6</f>
-        <v>73.555873508080026</v>
+        <v>77.785333333333327</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -684,7 +680,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>1.01541131265858</v>
+        <v>1.0001599999999999</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -695,7 +691,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0.99284889544052501</v>
+        <v>1.0001199999999999</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -706,7 +702,7 @@
         <v>27</v>
       </c>
       <c r="B14">
-        <v>0.99771860854582295</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
@@ -728,7 +724,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0.91738890416793295</v>
+        <v>0.891189942423528</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
